--- a/AAII_Financials/Yearly/IX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/IX_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="92">
   <si>
     <t>IX</t>
   </si>
@@ -656,220 +656,232 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44651</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44286</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43921</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43555</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43190</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42825</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42460</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42094</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41729</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41364</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40999</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>20948000</v>
+      </c>
+      <c r="E8" s="3">
         <v>19197700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>18606700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>20037500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>20653500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>20729900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>21192300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>21895700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>26950200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>18054200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>17413600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>18546600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>12289500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>9596900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>8794900</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>11900300</v>
+      </c>
+      <c r="E9" s="3">
         <v>11180600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10844700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>12210200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>12906200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>13384100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>13209600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>13981700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>18689200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>12783600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>12001200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>12031100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4307900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3945200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>4114000</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>9047600</v>
+      </c>
+      <c r="E10" s="3">
         <v>8017100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>7762000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7827300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>7747300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>7345800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>7982700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>7914000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>8261000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5270600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5412400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>6515500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>7981600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5651700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4680900</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -888,8 +900,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -935,9 +948,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -983,105 +999,114 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-224400</v>
+      </c>
+      <c r="E14" s="3">
         <v>-338400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-465800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-203900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-1095600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-149600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-557100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-260900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-397700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>22500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>98800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-10200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>214500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>162700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>286000</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2545800</v>
+      </c>
+      <c r="E15" s="3">
         <v>2668000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2408100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2559600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2638000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2856800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2827100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2667500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2635700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>36300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>37600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>40200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>32000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>27200</v>
       </c>
-      <c r="Q15" s="3" t="s">
+      <c r="R15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1097,104 +1122,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>16416900</v>
+      </c>
+      <c r="E17" s="3">
         <v>15557400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>14956500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>16480900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>17166500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>17661400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>17611000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>18096700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>23040200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>15796100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>15298700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>16048100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>10448600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>8225600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>7663100</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4531000</v>
+      </c>
+      <c r="E18" s="3">
         <v>3640400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3650200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3556600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3487000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3068500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3581300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3799000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3910000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2258100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2114900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2498500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1841000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1371300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1131800</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1213,134 +1245,141 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-812300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-358400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-235700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-151400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-174700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-87900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-615600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-268500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-497800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>606200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>761200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>435900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>758000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>197400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>47800</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>7889100</v>
+      </c>
+      <c r="E21" s="3">
         <v>6666700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>6294000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>6267500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>6299700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>6013200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>7024000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>6735100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>7043500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4581700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4658600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4915800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4500000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3197900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2702100</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1219300</v>
+      </c>
+      <c r="E22" s="3">
         <v>1128600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1244500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>961700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>562100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>706000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>919900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>757200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>705000</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
@@ -1356,105 +1395,114 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4348500</v>
+      </c>
+      <c r="E23" s="3">
         <v>3208500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3107200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2950200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4195300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2600000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3834100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3571200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4100600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2864300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2876100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2934500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2598900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1568700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1179600</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1466000</v>
+      </c>
+      <c r="E24" s="3">
         <v>860300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>868700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>716500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1536600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>820500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>983600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>619900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1072600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>970800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>884300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>759700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>890700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>488000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>403500</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1500,105 +1548,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2882500</v>
+      </c>
+      <c r="E26" s="3">
         <v>2348200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2238500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2233700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2658700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1779500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2850500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2951300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3028000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1893400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1991800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2174800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1708200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1080700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>776100</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2812300</v>
+      </c>
+      <c r="E27" s="3">
         <v>2347900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2288300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2184100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2613600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1739500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2813100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2921600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2948400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1841600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1912200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2001600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1642300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1015700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>754500</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1644,9 +1701,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1674,27 +1734,30 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N29" s="3">
+      <c r="N29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O29" s="3">
         <v>2500</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>68700</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>1500</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>24300</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1740,9 +1803,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1788,105 +1854,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>812300</v>
+      </c>
+      <c r="E32" s="3">
         <v>358400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>235700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>151400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>174700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>87900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>615600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>268500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>497800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-606200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-761200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-435900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-758000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-197400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-47800</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2812900</v>
+      </c>
+      <c r="E33" s="3">
         <v>2348100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2288400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2184100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2613600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1739500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2813100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2921600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2948400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1841600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1912200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2004100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1711000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1017300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>778800</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1932,110 +2007,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2812900</v>
+      </c>
+      <c r="E35" s="3">
         <v>2348100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2288400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2184100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2613600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1739500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2813100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2921600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2948400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1841600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1912200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2004100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1711000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1017300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>778800</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44651</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44286</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43921</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43555</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43190</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42825</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42460</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42094</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41729</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41364</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40999</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2054,8 +2138,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2074,86 +2159,90 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8395600</v>
+      </c>
+      <c r="E41" s="3">
         <v>8057400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6828300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9266700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7862900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8600800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>9132400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>10477700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>12440500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7637800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5963800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7788600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8440900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8558900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7113500</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>177900</v>
+      </c>
+      <c r="E42" s="3">
         <v>128700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>139000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>220800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>134000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>78400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>124100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>15400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>3977000</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -2169,135 +2258,144 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>37177900</v>
+      </c>
+      <c r="E43" s="3">
         <v>37921600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>36640000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>40837100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>43322400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>45357500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>47627000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>42437800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>40528000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1511100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1724100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2354900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1421300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>839600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>25505600</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1692900</v>
+      </c>
+      <c r="E44" s="3">
         <v>1530800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1503200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1271500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1149300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1285300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1171100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1044100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1045200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>794400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1028600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1412100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1246700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>377100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>720100</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>806000</v>
+      </c>
+      <c r="E45" s="3">
         <v>309200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>357000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>373100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>344200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>188300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>368900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>138600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>202500</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -2305,47 +2403,50 @@
         <v>0</v>
       </c>
       <c r="O45" s="3">
+        <v>0</v>
+      </c>
+      <c r="P45" s="3">
         <v>567100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>457400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>357500</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>48980800</v>
+      </c>
+      <c r="E46" s="3">
         <v>48718300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>46475600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>52985100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>53940800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>56670700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>59841800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>55219400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>58982900</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2361,138 +2462,147 @@
       <c r="Q46" s="3">
         <v>0</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R46" s="3">
+        <v>0</v>
+      </c>
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>29531300</v>
+        <v>28193000</v>
       </c>
       <c r="E47" s="3">
+        <v>29493700</v>
+      </c>
+      <c r="F47" s="3">
         <v>29193900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>28293500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>29997900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>29798800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>26065500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>22072800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>17878300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>44285000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>48935000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>59017800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>57838000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>59053000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>33575100</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6611600</v>
+      </c>
+      <c r="E48" s="3">
         <v>6927100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6779200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7319900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7493900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7708200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8252300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4963600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5157500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>12286200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>13203500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>14551100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4022800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3108900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1115000</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9006500</v>
+      </c>
+      <c r="E49" s="3">
         <v>8171900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8227500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9163100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>7928000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8902200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8420100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8025900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7876100</v>
       </c>
-      <c r="L49" s="3" t="s">
+      <c r="M49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
-      </c>
       <c r="N49" s="3">
         <v>0</v>
       </c>
@@ -2505,9 +2615,12 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2553,9 +2666,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2601,39 +2717,42 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>18859400</v>
+        <v>20133100</v>
       </c>
       <c r="E52" s="3">
+        <v>18896900</v>
+      </c>
+      <c r="F52" s="3">
         <v>16795200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>16890000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>17778000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>19200700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>18611800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>19283700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>17387700</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
       <c r="M52" s="3">
         <v>0</v>
       </c>
@@ -2647,11 +2766,14 @@
         <v>0</v>
       </c>
       <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3">
         <v>1114600</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2697,57 +2819,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>113221400</v>
+      </c>
+      <c r="E54" s="3">
         <v>112630900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>107911100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>115014900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>117517900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>122633000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>121443200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>109872000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>107584200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>75703000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>80797900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>97614100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>83075600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>76717000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>75328800</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2766,8 +2894,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2786,182 +2915,192 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2239000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2269100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2396600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2759600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2399800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2357300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2627500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2648500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2469800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1697100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1956700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2865500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4060900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2844500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2625800</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>9838800</v>
+        <v>10461200</v>
       </c>
       <c r="E58" s="3">
+        <v>3689200</v>
+      </c>
+      <c r="F58" s="3">
         <v>3820200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3852400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3687800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2993600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3539300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2950900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2934700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1910600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2569700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2429200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2835900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3824400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>4140100</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>10444200</v>
+        <v>12825000</v>
       </c>
       <c r="E59" s="3">
+        <v>710600</v>
+      </c>
+      <c r="F59" s="3">
         <v>1041200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>701400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1752900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>627400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>537600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>456000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>247400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13886600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>12915600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>13928600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>15538400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>12207200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1882000</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>22552000</v>
+        <v>25525100</v>
       </c>
       <c r="E60" s="3">
+        <v>6668900</v>
+      </c>
+      <c r="F60" s="3">
         <v>7258100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7313500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7840500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5978200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6704400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6055400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5651800</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -2977,87 +3116,93 @@
       <c r="Q60" s="3">
         <v>0</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R60" s="3">
+        <v>0</v>
+      </c>
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>33867400</v>
+        <v>32612400</v>
       </c>
       <c r="E61" s="3">
+        <v>40016900</v>
+      </c>
+      <c r="F61" s="3">
         <v>38918400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>41356500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>38786000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>42587500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>42276000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>37778400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>36029400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>25982600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>28936300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>35254000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>35347300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>36919300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>38578000</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>24436600</v>
+        <v>21767100</v>
       </c>
       <c r="E62" s="3">
+        <v>34170200</v>
+      </c>
+      <c r="F62" s="3">
         <v>31453900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>35535300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>39881300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>42342500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>40344700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>35844300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>35579900</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
@@ -3073,9 +3218,12 @@
       <c r="Q62" s="3">
         <v>0</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3121,9 +3269,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3169,9 +3320,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3217,57 +3371,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>84141800</v>
+      </c>
+      <c r="E66" s="3">
         <v>84749300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>81303000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>87818900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>89754700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>94575300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>92854800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>83132700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>81160800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>58801100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>63816300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>79255900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>65500000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>61776700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>62846900</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3286,8 +3446,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3333,9 +3494,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3381,9 +3545,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3429,9 +3596,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3477,57 +3647,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>22027700</v>
+      </c>
+      <c r="E72" s="3">
         <v>22403700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>21551200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>22977200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>23958000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>24815700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>25598600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>23062800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>21800100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>14002200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>13702200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>14267200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>13443200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>11862800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>10870100</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3573,9 +3749,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3621,9 +3800,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3669,57 +3851,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>28190900</v>
+      </c>
+      <c r="E76" s="3">
         <v>27311100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>26058400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>26656900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>26857500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>27382300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>27821100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>26144500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>25257000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>16901900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>16981700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>18358200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>17575700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>14940300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>12481900</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3765,110 +3953,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44651</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44286</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43921</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43555</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43190</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42825</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42460</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42094</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41729</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41364</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40999</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2812900</v>
+      </c>
+      <c r="E81" s="3">
         <v>2348100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2288400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2184100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2613600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1739500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2813100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2921600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2948400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1841600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1912200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2004100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1711000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1017300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>778800</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3887,56 +4084,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2285400</v>
+      </c>
+      <c r="E83" s="3">
         <v>2391500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2148900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2302200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2372500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2856800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2528000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2381000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2344200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1709800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1799700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1958300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1892800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1625700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1520800</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3982,9 +4183,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4030,9 +4234,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4078,9 +4285,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4126,9 +4336,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4174,57 +4387,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>8613400</v>
+      </c>
+      <c r="E89" s="3">
         <v>8682500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>8220600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>6868700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>9086200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>9967700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>9688200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>5303500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5355600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3935900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3752600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2197400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4314300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3557000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3010300</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4243,56 +4462,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8379800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-9066400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7939400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-8124900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-7553900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-6877900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-9227600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-9568600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-9898400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6671900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-7957400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-8434400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-8351300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-6831400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5451700</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4338,9 +4561,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4386,57 +4612,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7010300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-8746000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-9076100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-8263300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6660800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-10940300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-13666000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-7886900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4134600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1601500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4061100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3990300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1851800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>960400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>377500</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4455,56 +4687,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1074200</v>
+      </c>
+      <c r="E96" s="3">
         <v>905500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>660500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>799600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>818500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>860400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>964900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>798100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>685100</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-413200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-558800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-256900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-145400</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-88000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-77700</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4550,9 +4786,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4598,9 +4837,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4646,151 +4888,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1009600</v>
+      </c>
+      <c r="E100" s="3">
         <v>997200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-565100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3297200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2525000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>360600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2683100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1503900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1327700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-225500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-352800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1820600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2515100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-4246800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2879000</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>218600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-21000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>220000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>166800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>200400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>108300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-83400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-17200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>11500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-23200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-52400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>53200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>61900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>87600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-13600</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>812000</v>
+      </c>
+      <c r="E102" s="3">
         <v>912700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1200600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2069400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>100800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-503700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1378200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1096800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2560200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2085700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-713700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>80900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>9200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>358200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>495100</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
